--- a/Datos Experimentales/Data 24023.xlsx
+++ b/Datos Experimentales/Data 24023.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC16AFB-F974-4E7F-9BEF-6EA7906D8BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1065,11 +1076,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1098,14 +1106,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1430,10 +1447,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1441,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1449,7 +1467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1457,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1465,7 +1483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1473,7 +1491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1489,7 +1507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1497,7 +1515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1505,7 +1523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1513,7 +1531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1521,7 +1539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1529,7 +1547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1537,7 +1555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1545,7 +1563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1553,7 +1571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1561,7 +1579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1569,7 +1587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1577,7 +1595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1585,7 +1603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1593,7 +1611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1601,7 +1619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1609,7 +1627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1617,7 +1635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1625,7 +1643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1633,7 +1651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1641,7 +1659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1649,7 +1667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1657,7 +1675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1665,7 +1683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1673,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1681,7 +1699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1689,7 +1707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1697,7 +1715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1705,7 +1723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1713,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1721,7 +1739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1729,7 +1747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1737,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1745,7 +1763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1753,7 +1771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1761,7 +1779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1769,7 +1787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1777,7 +1795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1785,7 +1803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1793,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1801,7 +1819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1809,7 +1827,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1817,7 +1835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1825,7 +1843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1833,7 +1851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1841,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1849,7 +1867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1857,7 +1875,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1865,7 +1883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1873,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1881,7 +1899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1889,7 +1907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1897,7 +1915,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1905,7 +1923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1913,7 +1931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1921,7 +1939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1929,7 +1947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1937,7 +1955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1945,7 +1963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1953,7 +1971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1961,7 +1979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1969,7 +1987,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1977,7 +1995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1985,7 +2003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1993,7 +2011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -2001,7 +2019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -2009,7 +2027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -2017,7 +2035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2025,7 +2043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2033,7 +2051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2041,7 +2059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2049,7 +2067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2057,7 +2075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2065,7 +2083,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -2073,7 +2091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2081,7 +2099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2089,7 +2107,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2097,7 +2115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2105,7 +2123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2113,7 +2131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2121,7 +2139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2129,7 +2147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2137,7 +2155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2145,7 +2163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2153,7 +2171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2161,7 +2179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2169,7 +2187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2177,7 +2195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2185,7 +2203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2193,7 +2211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2201,7 +2219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2209,7 +2227,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2217,7 +2235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2225,7 +2243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2233,7 +2251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2241,7 +2259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2249,7 +2267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2257,7 +2275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2265,7 +2283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2273,7 +2291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2281,7 +2299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2289,7 +2307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2297,7 +2315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2305,7 +2323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2313,7 +2331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2321,7 +2339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2329,7 +2347,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2337,7 +2355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2345,7 +2363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2353,7 +2371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2361,7 +2379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2370,27 +2388,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B117"/>
+    <ignoredError sqref="A1:B117" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>287</v>
       </c>
@@ -2411,17 +2433,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>292</v>
       </c>
@@ -2432,7 +2456,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>295</v>
       </c>
@@ -2443,7 +2467,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>296</v>
       </c>
@@ -2454,29 +2478,29 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>297</v>
       </c>
       <c r="B4">
-        <v>0.7243055555555555</v>
+        <v>0.72430555555555554</v>
       </c>
       <c r="C4">
         <v>16.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>298</v>
       </c>
       <c r="B5">
-        <v>0.9743055555555555</v>
+        <v>0.97430555555555554</v>
       </c>
       <c r="C5">
         <v>17.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>299</v>
       </c>
@@ -2487,7 +2511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>300</v>
       </c>
@@ -2498,7 +2522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>301</v>
       </c>
@@ -2509,7 +2533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>302</v>
       </c>
@@ -2520,7 +2544,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>303</v>
       </c>
@@ -2531,7 +2555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>304</v>
       </c>
@@ -2542,7 +2566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>305</v>
       </c>
@@ -2553,7 +2577,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>306</v>
       </c>
@@ -2564,7 +2588,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>307</v>
       </c>
@@ -2575,7 +2599,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>308</v>
       </c>
@@ -2586,7 +2610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>309</v>
       </c>
@@ -2597,7 +2621,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>310</v>
       </c>
@@ -2608,7 +2632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>311</v>
       </c>
@@ -2616,10 +2640,10 @@
         <v>4.2243055555555555</v>
       </c>
       <c r="C18">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>312</v>
       </c>
@@ -2630,7 +2654,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>313</v>
       </c>
@@ -2641,7 +2665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>314</v>
       </c>
@@ -2652,7 +2676,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>315</v>
       </c>
@@ -2663,7 +2687,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>316</v>
       </c>
@@ -2674,7 +2698,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>317</v>
       </c>
@@ -2685,7 +2709,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>318</v>
       </c>
@@ -2696,7 +2720,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>319</v>
       </c>
@@ -2704,10 +2728,10 @@
         <v>6.2243055555555555</v>
       </c>
       <c r="C26">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>320</v>
       </c>
@@ -2715,10 +2739,10 @@
         <v>6.4743055555555555</v>
       </c>
       <c r="C27">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>321</v>
       </c>
@@ -2729,7 +2753,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>322</v>
       </c>
@@ -2740,7 +2764,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>323</v>
       </c>
@@ -2748,10 +2772,10 @@
         <v>7.2243055555555555</v>
       </c>
       <c r="C30">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>324</v>
       </c>
@@ -2762,7 +2786,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>325</v>
       </c>
@@ -2773,7 +2797,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>326</v>
       </c>
@@ -2784,95 +2808,95 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>327</v>
       </c>
       <c r="B34">
-        <v>8.224305555555556</v>
+        <v>8.2243055555555564</v>
       </c>
       <c r="C34">
         <v>16.5</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>328</v>
       </c>
       <c r="B35">
-        <v>8.474305555555556</v>
+        <v>8.4743055555555564</v>
       </c>
       <c r="C35">
         <v>16</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>329</v>
       </c>
       <c r="B36">
-        <v>8.724305555555556</v>
+        <v>8.7243055555555564</v>
       </c>
       <c r="C36">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>330</v>
       </c>
       <c r="B37">
-        <v>8.974305555555556</v>
+        <v>8.9743055555555564</v>
       </c>
       <c r="C37">
         <v>16.7</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>331</v>
       </c>
       <c r="B38">
-        <v>9.224305555555556</v>
+        <v>9.2243055555555564</v>
       </c>
       <c r="C38">
         <v>16.3</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>332</v>
       </c>
       <c r="B39">
-        <v>9.474305555555556</v>
+        <v>9.4743055555555564</v>
       </c>
       <c r="C39">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>333</v>
       </c>
       <c r="B40">
-        <v>9.724305555555556</v>
+        <v>9.7243055555555564</v>
       </c>
       <c r="C40">
         <v>15.8</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>334</v>
       </c>
       <c r="B41">
-        <v>9.974305555555556</v>
+        <v>9.9743055555555564</v>
       </c>
       <c r="C41">
         <v>16.7</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>335</v>
       </c>
@@ -2883,7 +2907,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>336</v>
       </c>
@@ -2891,10 +2915,10 @@
         <v>10.474305555555556</v>
       </c>
       <c r="C43">
-        <v>16.1</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>337</v>
       </c>
@@ -2905,7 +2929,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>338</v>
       </c>
@@ -2916,7 +2940,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>339</v>
       </c>
@@ -2927,7 +2951,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>340</v>
       </c>
@@ -2935,10 +2959,10 @@
         <v>11.474305555555556</v>
       </c>
       <c r="C47">
-        <v>16.1</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>341</v>
       </c>
@@ -2946,10 +2970,10 @@
         <v>11.724305555555556</v>
       </c>
       <c r="C48">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>342</v>
       </c>
@@ -2957,21 +2981,23 @@
         <v>11.974305555555556</v>
       </c>
       <c r="C49">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError sqref="A1:C49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>292</v>
       </c>
@@ -2982,7 +3008,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>295</v>
       </c>
@@ -2993,7 +3019,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>296</v>
       </c>
@@ -3004,29 +3030,29 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>297</v>
       </c>
       <c r="B4">
-        <v>0.7243055555555555</v>
+        <v>0.72430555555555554</v>
       </c>
       <c r="C4">
         <v>1085</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>298</v>
       </c>
       <c r="B5">
-        <v>0.9743055555555555</v>
+        <v>0.97430555555555554</v>
       </c>
       <c r="C5">
         <v>1084</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>299</v>
       </c>
@@ -3037,7 +3063,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>300</v>
       </c>
@@ -3048,7 +3074,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>301</v>
       </c>
@@ -3059,7 +3085,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>302</v>
       </c>
@@ -3070,7 +3096,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>303</v>
       </c>
@@ -3081,7 +3107,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>304</v>
       </c>
@@ -3092,7 +3118,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>305</v>
       </c>
@@ -3103,7 +3129,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>306</v>
       </c>
@@ -3114,7 +3140,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>307</v>
       </c>
@@ -3125,7 +3151,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>308</v>
       </c>
@@ -3136,7 +3162,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>309</v>
       </c>
@@ -3147,7 +3173,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>310</v>
       </c>
@@ -3158,7 +3184,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>311</v>
       </c>
@@ -3169,7 +3195,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>312</v>
       </c>
@@ -3180,7 +3206,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>313</v>
       </c>
@@ -3191,7 +3217,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>314</v>
       </c>
@@ -3202,7 +3228,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>315</v>
       </c>
@@ -3213,7 +3239,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>316</v>
       </c>
@@ -3224,7 +3250,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>317</v>
       </c>
@@ -3235,7 +3261,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>318</v>
       </c>
@@ -3246,7 +3272,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>319</v>
       </c>
@@ -3257,7 +3283,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>320</v>
       </c>
@@ -3268,7 +3294,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>321</v>
       </c>
@@ -3279,7 +3305,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>322</v>
       </c>
@@ -3290,7 +3316,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>323</v>
       </c>
@@ -3301,7 +3327,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>324</v>
       </c>
@@ -3312,7 +3338,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>325</v>
       </c>
@@ -3323,7 +3349,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>326</v>
       </c>
@@ -3334,95 +3360,95 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>327</v>
       </c>
       <c r="B34">
-        <v>8.224305555555556</v>
+        <v>8.2243055555555564</v>
       </c>
       <c r="C34">
         <v>1000</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>328</v>
       </c>
       <c r="B35">
-        <v>8.474305555555556</v>
+        <v>8.4743055555555564</v>
       </c>
       <c r="C35">
         <v>999</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>329</v>
       </c>
       <c r="B36">
-        <v>8.724305555555556</v>
+        <v>8.7243055555555564</v>
       </c>
       <c r="C36">
         <v>999</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>330</v>
       </c>
       <c r="B37">
-        <v>8.974305555555556</v>
+        <v>8.9743055555555564</v>
       </c>
       <c r="C37">
         <v>999</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>331</v>
       </c>
       <c r="B38">
-        <v>9.224305555555556</v>
+        <v>9.2243055555555564</v>
       </c>
       <c r="C38">
         <v>998</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>332</v>
       </c>
       <c r="B39">
-        <v>9.474305555555556</v>
+        <v>9.4743055555555564</v>
       </c>
       <c r="C39">
         <v>997</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>333</v>
       </c>
       <c r="B40">
-        <v>9.724305555555556</v>
+        <v>9.7243055555555564</v>
       </c>
       <c r="C40">
         <v>998</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>334</v>
       </c>
       <c r="B41">
-        <v>9.974305555555556</v>
+        <v>9.9743055555555564</v>
       </c>
       <c r="C41">
         <v>995</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>335</v>
       </c>
@@ -3433,7 +3459,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>336</v>
       </c>
@@ -3444,7 +3470,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>337</v>
       </c>
@@ -3455,7 +3481,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>338</v>
       </c>
@@ -3466,7 +3492,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>339</v>
       </c>
@@ -3477,7 +3503,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>340</v>
       </c>
@@ -3488,7 +3514,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>341</v>
       </c>
@@ -3499,7 +3525,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>342</v>
       </c>
@@ -3511,17 +3537,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError sqref="A1:C49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>292</v>
       </c>
@@ -3545,17 +3573,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3869,7 +3899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -3904,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45373.65069444444</v>
+        <v>45373.650694444441</v>
       </c>
       <c r="M2" t="s">
         <v>135</v>
@@ -3913,7 +3943,7 @@
         <v>136</v>
       </c>
       <c r="O2">
-        <v>45380.65069444444</v>
+        <v>45380.650694444441</v>
       </c>
       <c r="P2" t="s">
         <v>137</v>
@@ -3994,7 +4024,7 @@
         <v>145</v>
       </c>
       <c r="AS2">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="AT2">
         <v>12.6</v>
@@ -4093,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="BZ2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -4135,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="CN2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -4159,21 +4189,23 @@
         <v>0</v>
       </c>
       <c r="CV2">
-        <v>16.4</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CZ2"/>
+    <ignoredError sqref="A1:CZ2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4226,7 +4258,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4255,7 +4287,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9843</v>
       </c>
@@ -4290,7 +4322,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9843</v>
       </c>
@@ -4319,7 +4351,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9843</v>
       </c>
@@ -4333,7 +4365,7 @@
         <v>186</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>182</v>
@@ -4369,7 +4401,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9843</v>
       </c>
@@ -4383,7 +4415,7 @@
         <v>186</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>182</v>
@@ -4419,7 +4451,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9843</v>
       </c>
@@ -4454,7 +4486,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9843</v>
       </c>
@@ -4501,7 +4533,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9843</v>
       </c>
@@ -4530,7 +4562,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9843</v>
       </c>
@@ -4565,7 +4597,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9843</v>
       </c>
@@ -4600,7 +4632,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9843</v>
       </c>
@@ -4636,17 +4668,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4678,7 +4712,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4710,7 +4744,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9843</v>
       </c>
@@ -4742,7 +4776,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9843</v>
       </c>
@@ -4775,27 +4809,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4827,7 +4865,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4860,17 +4898,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4887,7 +4927,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4899,27 +4939,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4969,7 +5013,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4982,7 +5026,7 @@
       <c r="D2">
         <v>6818</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.77679398148</v>
       </c>
       <c r="F2" t="s">
@@ -5013,13 +5057,13 @@
         <v>244</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9843</v>
       </c>
@@ -5032,7 +5076,7 @@
       <c r="D3">
         <v>6818</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.77679398148</v>
       </c>
       <c r="F3" t="s">
@@ -5063,13 +5107,13 @@
         <v>244</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9843</v>
       </c>
@@ -5082,7 +5126,7 @@
       <c r="D4">
         <v>6818</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.77679398148</v>
       </c>
       <c r="F4" t="s">
@@ -5119,7 +5163,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9843</v>
       </c>
@@ -5132,7 +5176,7 @@
       <c r="D5">
         <v>6818</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.77679398148</v>
       </c>
       <c r="F5" t="s">
@@ -5169,7 +5213,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9843</v>
       </c>
@@ -5182,7 +5226,7 @@
       <c r="D6">
         <v>6818</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.77679398148</v>
       </c>
       <c r="F6" t="s">
@@ -5219,7 +5263,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9843</v>
       </c>
@@ -5232,7 +5276,7 @@
       <c r="D7">
         <v>6818</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.77679398148</v>
       </c>
       <c r="F7" t="s">
@@ -5269,7 +5313,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9843</v>
       </c>
@@ -5282,7 +5326,7 @@
       <c r="D8">
         <v>6818</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.77679398148</v>
       </c>
       <c r="F8" t="s">
@@ -5319,7 +5363,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9843</v>
       </c>
@@ -5332,8 +5376,8 @@
       <c r="D9">
         <v>6884</v>
       </c>
-      <c r="E9">
-        <v>45376.65771990741</v>
+      <c r="E9" s="1">
+        <v>45373.657719907409</v>
       </c>
       <c r="F9" t="s">
         <v>134</v>
@@ -5363,13 +5407,13 @@
         <v>244</v>
       </c>
       <c r="O9">
-        <v>7.8336</v>
+        <v>7.8335999999999997</v>
       </c>
       <c r="P9" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9843</v>
       </c>
@@ -5382,8 +5426,8 @@
       <c r="D10">
         <v>6884</v>
       </c>
-      <c r="E10">
-        <v>45376.65771990741</v>
+      <c r="E10" s="1">
+        <v>45373.657719907409</v>
       </c>
       <c r="F10" t="s">
         <v>134</v>
@@ -5419,7 +5463,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9843</v>
       </c>
@@ -5432,8 +5476,8 @@
       <c r="D11">
         <v>6884</v>
       </c>
-      <c r="E11">
-        <v>45376.65771990741</v>
+      <c r="E11" s="1">
+        <v>45373.657719907409</v>
       </c>
       <c r="F11" t="s">
         <v>134</v>
@@ -5463,13 +5507,13 @@
         <v>244</v>
       </c>
       <c r="O11">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="P11" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9843</v>
       </c>
@@ -5482,8 +5526,8 @@
       <c r="D12">
         <v>6884</v>
       </c>
-      <c r="E12">
-        <v>45376.65771990741</v>
+      <c r="E12" s="1">
+        <v>45373.657719907409</v>
       </c>
       <c r="F12" t="s">
         <v>134</v>
@@ -5519,7 +5563,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9843</v>
       </c>
@@ -5532,8 +5576,8 @@
       <c r="D13">
         <v>6884</v>
       </c>
-      <c r="E13">
-        <v>45376.65771990741</v>
+      <c r="E13" s="1">
+        <v>45373.657719907409</v>
       </c>
       <c r="F13" t="s">
         <v>134</v>
@@ -5569,7 +5613,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9843</v>
       </c>
@@ -5582,8 +5626,8 @@
       <c r="D14">
         <v>6884</v>
       </c>
-      <c r="E14">
-        <v>45376.65771990741</v>
+      <c r="E14" s="1">
+        <v>45373.657719907409</v>
       </c>
       <c r="F14" t="s">
         <v>134</v>
@@ -5613,13 +5657,13 @@
         <v>244</v>
       </c>
       <c r="O14">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="P14" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9843</v>
       </c>
@@ -5632,8 +5676,8 @@
       <c r="D15">
         <v>6884</v>
       </c>
-      <c r="E15">
-        <v>45376.65771990741</v>
+      <c r="E15" s="1">
+        <v>45373.657719907409</v>
       </c>
       <c r="F15" t="s">
         <v>134</v>
@@ -5669,7 +5713,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9843</v>
       </c>
@@ -5682,8 +5726,8 @@
       <c r="D16">
         <v>7166</v>
       </c>
-      <c r="E16">
-        <v>45384.85260416666</v>
+      <c r="E16" s="1">
+        <v>45384.852604166663</v>
       </c>
       <c r="F16" t="s">
         <v>134</v>
@@ -5719,7 +5763,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9843</v>
       </c>
@@ -5732,7 +5776,7 @@
       <c r="D17">
         <v>7232</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>45386.858194444445</v>
       </c>
       <c r="F17" t="s">
@@ -5769,7 +5813,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9843</v>
       </c>
@@ -5782,8 +5826,8 @@
       <c r="D18">
         <v>7285</v>
       </c>
-      <c r="E18">
-        <v>45387.75166666666</v>
+      <c r="E18" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F18" t="s">
         <v>134</v>
@@ -5819,7 +5863,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9843</v>
       </c>
@@ -5832,8 +5876,8 @@
       <c r="D19">
         <v>7285</v>
       </c>
-      <c r="E19">
-        <v>45387.75166666666</v>
+      <c r="E19" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F19" t="s">
         <v>134</v>
@@ -5869,7 +5913,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9843</v>
       </c>
@@ -5882,8 +5926,8 @@
       <c r="D20">
         <v>7285</v>
       </c>
-      <c r="E20">
-        <v>45387.75166666666</v>
+      <c r="E20" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F20" t="s">
         <v>134</v>
@@ -5919,7 +5963,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9843</v>
       </c>
@@ -5932,8 +5976,8 @@
       <c r="D21">
         <v>7285</v>
       </c>
-      <c r="E21">
-        <v>45387.75166666666</v>
+      <c r="E21" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F21" t="s">
         <v>134</v>
@@ -5969,7 +6013,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9843</v>
       </c>
@@ -5982,8 +6026,8 @@
       <c r="D22">
         <v>7285</v>
       </c>
-      <c r="E22">
-        <v>45387.75166666666</v>
+      <c r="E22" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F22" t="s">
         <v>134</v>
@@ -6019,7 +6063,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9843</v>
       </c>
@@ -6032,8 +6076,8 @@
       <c r="D23">
         <v>7285</v>
       </c>
-      <c r="E23">
-        <v>45387.75166666666</v>
+      <c r="E23" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F23" t="s">
         <v>134</v>
@@ -6069,7 +6113,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9843</v>
       </c>
@@ -6082,8 +6126,8 @@
       <c r="D24">
         <v>7285</v>
       </c>
-      <c r="E24">
-        <v>45387.75166666666</v>
+      <c r="E24" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F24" t="s">
         <v>134</v>
@@ -6119,7 +6163,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9843</v>
       </c>
@@ -6132,8 +6176,8 @@
       <c r="D25">
         <v>7285</v>
       </c>
-      <c r="E25">
-        <v>45387.75166666666</v>
+      <c r="E25" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F25" t="s">
         <v>134</v>
@@ -6169,7 +6213,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9843</v>
       </c>
@@ -6182,8 +6226,8 @@
       <c r="D26">
         <v>7285</v>
       </c>
-      <c r="E26">
-        <v>45387.75166666666</v>
+      <c r="E26" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F26" t="s">
         <v>134</v>
@@ -6219,7 +6263,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9843</v>
       </c>
@@ -6232,8 +6276,8 @@
       <c r="D27">
         <v>7285</v>
       </c>
-      <c r="E27">
-        <v>45387.75166666666</v>
+      <c r="E27" s="1">
+        <v>45387.751666666663</v>
       </c>
       <c r="F27" t="s">
         <v>134</v>
@@ -6269,7 +6313,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9843</v>
       </c>
@@ -6282,8 +6326,8 @@
       <c r="D28">
         <v>7458</v>
       </c>
-      <c r="E28">
-        <v>45392.80699074074</v>
+      <c r="E28" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F28" t="s">
         <v>134</v>
@@ -6319,7 +6363,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9843</v>
       </c>
@@ -6332,8 +6376,8 @@
       <c r="D29">
         <v>7458</v>
       </c>
-      <c r="E29">
-        <v>45392.80699074074</v>
+      <c r="E29" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F29" t="s">
         <v>134</v>
@@ -6369,7 +6413,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9843</v>
       </c>
@@ -6382,8 +6426,8 @@
       <c r="D30">
         <v>7458</v>
       </c>
-      <c r="E30">
-        <v>45392.80699074074</v>
+      <c r="E30" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F30" t="s">
         <v>134</v>
@@ -6419,7 +6463,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9843</v>
       </c>
@@ -6432,8 +6476,8 @@
       <c r="D31">
         <v>7458</v>
       </c>
-      <c r="E31">
-        <v>45392.80699074074</v>
+      <c r="E31" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F31" t="s">
         <v>134</v>
@@ -6469,7 +6513,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9843</v>
       </c>
@@ -6482,8 +6526,8 @@
       <c r="D32">
         <v>7458</v>
       </c>
-      <c r="E32">
-        <v>45392.80699074074</v>
+      <c r="E32" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F32" t="s">
         <v>134</v>
@@ -6519,7 +6563,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9843</v>
       </c>
@@ -6532,8 +6576,8 @@
       <c r="D33">
         <v>7458</v>
       </c>
-      <c r="E33">
-        <v>45392.80699074074</v>
+      <c r="E33" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F33" t="s">
         <v>134</v>
@@ -6569,7 +6613,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9843</v>
       </c>
@@ -6582,8 +6626,8 @@
       <c r="D34">
         <v>7458</v>
       </c>
-      <c r="E34">
-        <v>45392.80699074074</v>
+      <c r="E34" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F34" t="s">
         <v>134</v>
@@ -6619,7 +6663,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9843</v>
       </c>
@@ -6632,8 +6676,8 @@
       <c r="D35">
         <v>7458</v>
       </c>
-      <c r="E35">
-        <v>45392.80699074074</v>
+      <c r="E35" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F35" t="s">
         <v>134</v>
@@ -6669,7 +6713,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9843</v>
       </c>
@@ -6682,8 +6726,8 @@
       <c r="D36">
         <v>7458</v>
       </c>
-      <c r="E36">
-        <v>45392.80699074074</v>
+      <c r="E36" s="1">
+        <v>45392.806990740741</v>
       </c>
       <c r="F36" t="s">
         <v>134</v>
@@ -6719,7 +6763,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9843</v>
       </c>
@@ -6732,7 +6776,7 @@
       <c r="D37">
         <v>7459</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F37" t="s">
@@ -6769,7 +6813,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9843</v>
       </c>
@@ -6782,7 +6826,7 @@
       <c r="D38">
         <v>7459</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F38" t="s">
@@ -6813,13 +6857,13 @@
         <v>244</v>
       </c>
       <c r="O38">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P38" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9843</v>
       </c>
@@ -6832,7 +6876,7 @@
       <c r="D39">
         <v>7459</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F39" t="s">
@@ -6869,7 +6913,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>9843</v>
       </c>
@@ -6882,7 +6926,7 @@
       <c r="D40">
         <v>7459</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F40" t="s">
@@ -6919,7 +6963,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9843</v>
       </c>
@@ -6932,7 +6976,7 @@
       <c r="D41">
         <v>7459</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F41" t="s">
@@ -6963,13 +7007,13 @@
         <v>244</v>
       </c>
       <c r="O41">
-        <v>0.071</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="P41" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9843</v>
       </c>
@@ -6982,7 +7026,7 @@
       <c r="D42">
         <v>7459</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F42" t="s">
@@ -7019,7 +7063,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>9843</v>
       </c>
@@ -7032,7 +7076,7 @@
       <c r="D43">
         <v>7459</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F43" t="s">
@@ -7063,13 +7107,13 @@
         <v>244</v>
       </c>
       <c r="O43">
-        <v>0.071</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="P43" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>9843</v>
       </c>
@@ -7082,7 +7126,7 @@
       <c r="D44">
         <v>7459</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F44" t="s">
@@ -7119,7 +7163,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>9843</v>
       </c>
@@ -7132,7 +7176,7 @@
       <c r="D45">
         <v>7459</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F45" t="s">
@@ -7169,7 +7213,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9843</v>
       </c>
@@ -7182,7 +7226,7 @@
       <c r="D46">
         <v>7459</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="1">
         <v>45392.807708333334</v>
       </c>
       <c r="F46" t="s">
@@ -7220,8 +7264,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P46"/>
+    <ignoredError sqref="A1:P8 A16:P46 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24023.xlsx
+++ b/Datos Experimentales/Data 24023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC16AFB-F974-4E7F-9BEF-6EA7906D8BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57C8A7E-E8AF-4AFB-ABCF-8089BF429351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1449,9 +1449,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B117"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2398,7 +2398,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2410,9 +2410,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>287</v>
       </c>
@@ -2443,9 +2443,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>292</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>295</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>296</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>297</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>298</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>299</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>300</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>301</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>302</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>303</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>304</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>305</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>306</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>307</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>308</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>309</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>310</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>311</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>312</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>313</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>314</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>315</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>316</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>317</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>318</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>319</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>320</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>321</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>322</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>323</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>324</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>325</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>326</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>327</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>328</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>329</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>330</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>331</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>332</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>333</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>334</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>335</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>336</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>337</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>338</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>339</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>340</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>341</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>342</v>
       </c>
@@ -2995,9 +2995,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>292</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>295</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>296</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>297</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>298</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>299</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>300</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>301</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>302</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>303</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>304</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>305</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>306</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>307</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>308</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>309</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>310</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>311</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>312</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>313</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>314</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>315</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>316</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>317</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>318</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>319</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>320</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>321</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>322</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>323</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>324</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>325</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>326</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>327</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>328</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>329</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>330</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>331</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>332</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>333</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>334</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>335</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>336</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>337</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>338</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>339</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>340</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>341</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>342</v>
       </c>
@@ -3547,9 +3547,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>292</v>
       </c>
@@ -3583,9 +3583,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:104" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:104" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4203,9 +4203,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9843</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9843</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9843</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9843</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9843</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9843</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9843</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9843</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9843</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9843</v>
       </c>
@@ -4678,9 +4678,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9843</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9843</v>
       </c>
@@ -4819,7 +4819,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4831,9 +4831,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4908,9 +4908,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -4949,7 +4949,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4961,9 +4961,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9843</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9843</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9843</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9843</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9843</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9843</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9843</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9843</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9843</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9843</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9843</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9843</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9843</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9843</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9843</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9843</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9843</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9843</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9843</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9843</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9843</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9843</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9843</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9843</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9843</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9843</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9843</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>252</v>
       </c>
       <c r="J28" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K28" t="s">
         <v>254</v>
@@ -6363,7 +6363,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9843</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>252</v>
       </c>
       <c r="J29" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K29" t="s">
         <v>268</v>
@@ -6413,7 +6413,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9843</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>252</v>
       </c>
       <c r="J30" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K30" t="s">
         <v>270</v>
@@ -6463,7 +6463,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9843</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>252</v>
       </c>
       <c r="J31" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K31" t="s">
         <v>264</v>
@@ -6513,7 +6513,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9843</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>252</v>
       </c>
       <c r="J32" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K32" t="s">
         <v>275</v>
@@ -6563,7 +6563,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9843</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>252</v>
       </c>
       <c r="J33" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K33" t="s">
         <v>277</v>
@@ -6613,7 +6613,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9843</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>252</v>
       </c>
       <c r="J34" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K34" t="s">
         <v>248</v>
@@ -6663,7 +6663,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9843</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>252</v>
       </c>
       <c r="J35" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K35" t="s">
         <v>259</v>
@@ -6713,7 +6713,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9843</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>252</v>
       </c>
       <c r="J36" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="K36" t="s">
         <v>261</v>
@@ -6763,7 +6763,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9843</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9843</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9843</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>9843</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9843</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9843</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>9843</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>9843</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>9843</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9843</v>
       </c>
@@ -7266,7 +7266,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P8 A16:P46 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P8 A16:P27 A9:D9 F9:P9 A10:D15 F10:P15 A37:P46 A28:I36 K28:P36" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>